--- a/final_outputs/excel_tables/table_subsample_summary.xlsx
+++ b/final_outputs/excel_tables/table_subsample_summary.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q0.10, q0.25, q0.50, q0.75, q0.90</t>
+          <t>q0.25, q0.50, q0.75, q0.90</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q0.10, q0.25, q0.50</t>
+          <t>q0.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q0.25, q0.50, q0.75, q0.90</t>
+          <t>q0.25, q0.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q0.25, q0.50, q0.75</t>
+          <t>q0.50, q0.75</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -765,17 +765,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>q0.10</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Negative effect in significant quantiles.</t>
+          <t>No statistically significant effect across quantiles.</t>
         </is>
       </c>
     </row>
@@ -792,17 +792,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>q0.75</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Negative effect in significant quantiles.</t>
+          <t>No statistically significant effect across quantiles.</t>
         </is>
       </c>
     </row>
@@ -819,17 +819,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>q0.10, q0.90</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Negative effect in significant quantiles.</t>
+          <t>No statistically significant effect across quantiles.</t>
         </is>
       </c>
     </row>
@@ -846,17 +846,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>q0.90</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>n.s.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Positive effect in significant quantiles.</t>
+          <t>No statistically significant effect across quantiles.</t>
         </is>
       </c>
     </row>

--- a/final_outputs/excel_tables/table_subsample_summary.xlsx
+++ b/final_outputs/excel_tables/table_subsample_summary.xlsx
@@ -765,17 +765,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>q0.10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>n.s.</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>No statistically significant effect across quantiles.</t>
+          <t>Negative effect in significant quantiles.</t>
         </is>
       </c>
     </row>
@@ -792,17 +792,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>q0.10, q0.50, q0.75, q0.90</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>n.s.</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>No statistically significant effect across quantiles.</t>
+          <t>Negative effect in significant quantiles.</t>
         </is>
       </c>
     </row>
@@ -819,17 +819,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>q0.10, q0.25, q0.50, q0.75, q0.90</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>n.s.</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>No statistically significant effect across quantiles.</t>
+          <t>Negative effect in significant quantiles.</t>
         </is>
       </c>
     </row>
@@ -846,17 +846,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>q0.10, q0.90</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>n.s.</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>No statistically significant effect across quantiles.</t>
+          <t>Positive effect in significant quantiles.</t>
         </is>
       </c>
     </row>
